--- a/OILmap/refined.xlsx
+++ b/OILmap/refined.xlsx
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1975,6 +1975,90 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Russia (Black Sea)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>~50% of Israel’s refined imports; ~1% of Russia’s product exports</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Novorossiysk -&gt; Turkish Straits -&gt; Mediterranean -&gt; Haifa/Ashdod</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Oil Change International (Russia ~half of Israel’s refined imports, Nov 2023–Oct 2025); Russia-side % estimated</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>~10% of Israel’s refined imports; ~1% of US product exports</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Gulf Coast -&gt; Gibraltar -&gt; Mediterranean -&gt; Israel</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Oil Change International (USA sole JP-8 military jet-fuel supplier); % estimated</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1986,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2161,15 +2245,15 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Oil Change International: USA is the sole JP-8 military jet-fuel supplier to Israel; % estimated</t>
         </is>
       </c>
     </row>
@@ -2181,20 +2265,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -2211,15 +2295,15 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ARA hub (Netherlands)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Pattern: East Coast gasoline blendstock; % estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -2236,15 +2320,15 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>ARA hub (Netherlands)</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: East Coast gasoline blendstock; % estimated</t>
         </is>
       </c>
     </row>
@@ -2261,11 +2345,11 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2286,40 +2370,40 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Pattern: India became a top EU diesel supplier after the 2023 Russian product embargo; % estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -2336,15 +2420,15 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern: India became a top EU diesel supplier after the 2023 Russian product embargo; % estimated</t>
         </is>
       </c>
     </row>
@@ -2361,15 +2445,15 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -2386,11 +2470,11 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -2411,11 +2495,11 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -2436,11 +2520,11 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -2461,15 +2545,15 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Other Asia</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -2481,20 +2565,20 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Other Asia</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Pattern: India is a top-2 global LPG importer, Gulf-sourced; % estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -2511,15 +2595,15 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern: India is a top-2 global LPG importer, Gulf-sourced; % estimated</t>
         </is>
       </c>
     </row>
@@ -2536,11 +2620,11 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -2561,15 +2645,15 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -2586,40 +2670,40 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Turkey became Russia’s largest diesel buyer post-2022; % estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -2636,15 +2720,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern: Turkey became Russia’s largest diesel buyer post-2022; % estimated</t>
         </is>
       </c>
     </row>
@@ -2661,11 +2745,11 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Asia (incl. UAE transshipment)</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -2686,15 +2770,15 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Asia (incl. UAE transshipment)</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Brazil became a major Russian diesel buyer post-2022; % estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -2711,15 +2795,15 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Other / undisclosed</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder (shadow-fleet cargoes are hard to track)</t>
+          <t>Pattern: Brazil became a major Russian diesel buyer post-2022; % estimated</t>
         </is>
       </c>
     </row>
@@ -2731,27 +2815,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Net exporter; no meaningful tracked refined imports</t>
+          <t>Estimated: ~half of Israel’s small refined-import volume</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2761,40 +2845,40 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Other / undisclosed</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder (shadow-fleet cargoes are hard to track)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Net exporter; no meaningful tracked refined imports</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2895,11 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2836,15 +2920,15 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2945,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -2886,15 +2970,15 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -2911,15 +2995,15 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Other Asia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -2931,27 +3015,27 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Net exporter; no meaningful tracked refined imports</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2961,40 +3045,40 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Other Asia</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Net exporter; no meaningful tracked refined imports</t>
         </is>
       </c>
     </row>
@@ -3011,15 +3095,15 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3120,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -3044,7 +3128,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3056,27 +3140,27 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Net exporter; no meaningful tracked refined imports</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3086,40 +3170,40 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Net exporter; no meaningful tracked refined imports</t>
         </is>
       </c>
     </row>
@@ -3136,11 +3220,11 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3161,15 +3245,15 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3181,20 +3265,20 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Fujairah blends discounted Russian-origin fuel oil for re-export; % estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3206,20 +3290,20 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3236,65 +3320,65 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern: Fujairah blends discounted Russian-origin fuel oil for re-export; % estimated</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3311,15 +3395,15 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3336,15 +3420,15 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3361,11 +3445,11 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3386,11 +3470,11 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3411,15 +3495,15 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Other Asia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -3431,20 +3515,20 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -3456,20 +3540,20 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Other Asia</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3486,15 +3570,15 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3511,15 +3595,15 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Pattern: discounted Russian barrels reach the hub for blending; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -3536,65 +3620,65 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern: discounted Russian barrels reach the hub for blending; % estimated</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3611,11 +3695,11 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -3636,15 +3720,15 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3745,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -3669,7 +3753,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3681,20 +3765,20 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -3706,20 +3790,20 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3736,11 +3820,11 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -3761,15 +3845,15 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3786,65 +3870,65 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3861,15 +3945,15 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -3886,15 +3970,15 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -3906,16 +3990,16 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3931,20 +4015,20 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -3961,11 +4045,11 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3986,65 +4070,65 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4061,15 +4145,15 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -4086,11 +4170,11 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -4111,11 +4195,11 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -4136,11 +4220,11 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -4161,15 +4245,15 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Other Asia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -4181,20 +4265,20 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Pattern: naphtha/LPG feedstock from the Gulf; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -4206,20 +4290,20 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other Asia</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4320,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
@@ -4244,28 +4328,28 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern: naphtha/LPG feedstock from the Gulf; % estimated</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -4276,25 +4360,25 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4311,15 +4395,15 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -4336,11 +4420,11 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -4361,11 +4445,11 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -4386,15 +4470,15 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Other Asia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -4406,20 +4490,20 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Pattern: discounted fuel oil feeds independent "teapot" refiners; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -4431,20 +4515,20 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Malaysia (transshipment)</t>
+          <t>Other Asia</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4461,15 +4545,15 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: discounted fuel oil feeds independent "teapot" refiners; % estimated</t>
         </is>
       </c>
     </row>
@@ -4486,15 +4570,15 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>Malaysia (transshipment)</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -4511,47 +4595,47 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4561,15 +4645,15 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Pattern: overwhelming US dependence for gasoline/diesel; % estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4581,52 +4665,52 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Pattern: overwhelming US dependence for gasoline/diesel; % estimated</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4636,15 +4720,15 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4656,20 +4740,20 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
@@ -4686,15 +4770,15 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -4711,47 +4795,47 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -4761,15 +4845,15 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4781,20 +4865,20 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
@@ -4811,15 +4895,15 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -4836,15 +4920,15 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -4861,11 +4945,11 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -4886,47 +4970,47 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -4936,15 +5020,15 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -4956,20 +5040,20 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
@@ -4986,15 +5070,15 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -5011,11 +5095,11 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
@@ -5036,11 +5120,11 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
@@ -5061,65 +5145,65 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Dangote supplies the regional market; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -5136,15 +5220,15 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: Dangote supplies the regional market; % estimated</t>
         </is>
       </c>
     </row>
@@ -5161,15 +5245,15 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -5181,20 +5265,20 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ARA hub (Netherlands)</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Pattern: the historic gasoline import route, now shrinking; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5290,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
@@ -5219,7 +5303,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -5236,15 +5320,15 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>ARA hub (Netherlands)</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: the historic gasoline import route, now shrinking; % estimated</t>
         </is>
       </c>
     </row>
@@ -5261,52 +5345,52 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Pattern: much-reported re-export route post-embargo; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5315,7 +5399,7 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -5331,20 +5415,20 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Turkey is Russia’s largest diesel buyer; % estimated</t>
+          <t>Pattern: much-reported re-export route post-embargo; % estimated</t>
         </is>
       </c>
     </row>
@@ -5356,20 +5440,20 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -5386,15 +5470,15 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: Turkey is Russia’s largest diesel buyer; % estimated</t>
         </is>
       </c>
     </row>
@@ -5411,47 +5495,47 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -5461,47 +5545,47 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Not tracked as a refined exporter on this map (refines mostly for its own market)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -5511,22 +5595,22 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Oil Change International: Russia supplied nearly half of refined products, Nov 2023–Oct 2025</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -5536,47 +5620,47 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Greece / Italy / Cyprus (EU refiners)</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Oil Change International names these as other product suppliers; % estimated</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Oil Change International: sole JP-8 supplier; % estimated</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -5586,47 +5670,47 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -5636,22 +5720,22 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -5661,22 +5745,22 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -5686,72 +5770,72 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Not tracked as a refined exporter on this map</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>ARA hub (Netherlands, Belgium)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -5761,22 +5845,22 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -5786,22 +5870,22 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -5811,11 +5895,11 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
@@ -5826,7 +5910,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -5836,47 +5920,47 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -5886,22 +5970,22 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Not tracked as a refined exporter on this map</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -5911,11 +5995,11 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ARA hub (Netherlands, Belgium)</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -5926,7 +6010,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5936,11 +6020,11 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>ARA hub (Netherlands)</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
@@ -5951,7 +6035,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -5961,47 +6045,47 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Gulf refiners</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Import hub, not an exporter</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -6011,72 +6095,72 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Pattern: India replaced much of the lost Russian diesel; % estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -6086,22 +6170,22 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -6111,22 +6195,22 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>ARA hub (Netherlands)</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Al-Zour volumes aimed at Europe; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>EU (27) (hub marker)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -6136,15 +6220,15 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Pattern: re-export route for Russian-origin barrels; % estimated</t>
+          <t>Estimated remainder</t>
         </is>
       </c>
     </row>
@@ -6156,12 +6240,12 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
@@ -6169,7 +6253,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Embargoed since Feb 2023 — direct seaborne imports are ~zero</t>
+          <t>Import hub, not an exporter</t>
         </is>
       </c>
     </row>
@@ -6186,61 +6270,61 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Other suppliers</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern: India replaced much of the lost Russian diesel; % estimated</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6335,21 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -6276,96 +6360,96 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: Al-Zour volumes aimed at Europe; % estimated</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern: re-export route for Russian-origin barrels; % estimated</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Embargoed since Feb 2023 — direct seaborne imports are ~zero</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Singapore (hub marker)</t>
+          <t>EU (27) (hub marker)</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Other Asia</t>
+          <t>Other suppliers</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
@@ -6381,16 +6465,16 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Gulf refiners</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
@@ -6406,12 +6490,12 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
@@ -6419,7 +6503,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
         </is>
       </c>
     </row>
@@ -6431,12 +6515,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
@@ -6456,12 +6540,12 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
@@ -6469,7 +6553,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Pattern: discounted Russian barrels reach the hub for blending; % estimated</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -6481,25 +6565,201 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Other Asia</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Estimated remainder</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Gulf refiners</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Pattern is well established; exact % is this project’s estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Pattern: discounted Russian barrels reach the hub for blending; % estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Singapore (hub marker)</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="D180" s="2" t="n">
+      <c r="D187" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Estimated remainder</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
+    <row r="188"/>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>Note: every Export block sums to 100% (or is a single 0%/"None" row for countries not tracked as refined exporters), and every Import block sums to 100% (or 0% for net exporters). "Pattern is well established" means the direction and dominance of that flow is real and well documented; the exact percentage is this project’s estimate. "Estimated" means the share is a judgement call made to complete the 100% picture.</t>
         </is>
@@ -6648,7 +6908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6739,6 +6999,18 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Added Sept 2026 as an importer (gray). Israel refines most of its own fuel (Bazan/Haifa, Paz/Ashdod) from imported crude, so product imports are a top-up — they surged after Iranian missiles shut Bazan in June 2025. Arrows drawn: Russia (~50%) and USA (~10%, JP-8). Greece/Italy/Cyprus (~25%) appear in the hover only: the EU hub is import-only on this map. To make room: US exports Other 25 -&gt; 24, Russia Other/undisclosed 21 -&gt; 20 (+ Israel 1 each).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OILmap/refined.xlsx
+++ b/OILmap/refined.xlsx
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Post-2023 embargo shift well documented; % estimated</t>
+          <t>Post-2023 embargo shift well documented; % estimated. Short route; since the Red Sea attacks (late 2023) most cargoes go round the Cape — see the Cape diversion row.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>None (Bosphorus not needed)</t>
+          <t>Turkish Straits (to Marmara / Aegean refineries)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Primorsk/Ust-Luga -&gt; West Africa</t>
+          <t>Primorsk/Ust-Luga -&gt; Danish Straits -&gt; North Sea -&gt; Atlantic -&gt; West Africa</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Danish Straits</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Primorsk/Ust-Luga -&gt; Brazil</t>
+          <t>Primorsk/Ust-Luga -&gt; Danish Straits -&gt; North Sea -&gt; Atlantic -&gt; Brazil</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Danish Straits</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Black Sea -&gt; Suez -&gt; Bab-el-Mandeb -&gt; Arabian Sea -&gt; Fujairah</t>
+          <t>Black Sea -&gt; Turkish Straits -&gt; Suez -&gt; Bab-el-Mandeb -&gt; Arabian Sea -&gt; Fujairah</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Suez Canal, Bab-el-Mandeb</t>
+          <t>Turkish Straits, Suez Canal, Bab-el-Mandeb</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Pattern well established; % estimated</t>
+          <t>Pattern well established; % estimated. Short route; since the Red Sea attacks (late 2023) most cargoes go round the Cape — see the Cape diversion row.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Turkish Straits</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2054,6 +2054,384 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>EU (Cape diversion)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Same ~25% India -&gt; EU flow, re-routed</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Jamnagar -&gt; Cape of Good Hope -&gt; West Africa coast -&gt; EU hub</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Cape of Good Hope</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Dotted</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Red Sea diversion since late 2023 well documented; share of cargoes estimated</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Gulf refiners</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>EU (Cape diversion)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Same Gulf -&gt; EU flow, re-routed</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Gulf -&gt; Hormuz -&gt; Cape of Good Hope -&gt; West Africa coast -&gt; EU hub</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Hormuz, Cape of Good Hope</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Dotted</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Red Sea diversion since late 2023 well documented; share of cargoes estimated</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>~12% of Brazil’s product imports</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Jamnagar -&gt; Cape of Good Hope -&gt; Brazil</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Cape of Good Hope</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>West Africa (Nigeria)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>~10% of Nigeria’s product imports; part of ~18% to Africa</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Jamnagar -&gt; Cape of Good Hope -&gt; West Africa</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Cape of Good Hope</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>USA (East Coast)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>~7% of India’s product exports (~6% of US imports)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Jamnagar -&gt; Cape of Good Hope -&gt; Atlantic -&gt; US East Coast</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Cape of Good Hope</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Asia (South Korea, China)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>~10% of US product exports; ~30% of South Korea’s and ~15% of China’s imports</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Gulf Coast -&gt; Panama Canal -&gt; Pacific -&gt; South Korea / China (drawn as 3 segments, wrapping at the map edge)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Panama Canal</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>~12% of Indonesia’s product imports</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Jamnagar -&gt; Strait of Malacca -&gt; Jakarta</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Malacca</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Gulf refiners (Saudi Arabia, UAE)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>UAE ~30% + Saudi ~25% of India’s product imports</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Gulf -&gt; Hormuz -&gt; India west coast</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Hormuz</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Russia (Black Sea)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>~10% of Singapore’s imports; part of ~20% to Asia</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Black Sea -&gt; Turkish Straits -&gt; Suez -&gt; Bab-el-Mandeb -&gt; Malacca -&gt; Singapore</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Turkish Straits, Suez Canal, Bab-el-Mandeb, Strait of Malacca</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Estimated (from Export-Import % sheet)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>~Sept 2026</t>
         </is>
@@ -6757,7 +7135,6 @@
         </is>
       </c>
     </row>
-    <row r="188"/>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
@@ -6776,13 +7153,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6806,6 +7184,11 @@
           <t>Used by (refined flows)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Controlled by</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6821,7 +7204,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Everything leaving the Gulf refiners (Jazan, Al-Zour, Ruwais).</t>
+          <t>Gulf refiners -&gt; EU (Suez route and Cape diversion), East Africa, Asia, India</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Iran (north shore) and Oman (Musandam, south shore) — the shipping lanes run through Omani waters.</t>
         </is>
       </c>
     </row>
@@ -6839,7 +7227,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Red Sea entrance — Gulf and Indian diesel heading for Suez/EU; Russian products heading to Fujairah.</t>
+          <t>India -&gt; EU; Gulf refiners -&gt; EU; Russia -&gt; UAE (Fujairah); Russia -&gt; Singapore</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yemen (east shore) and Djibouti (west shore), with Eritrea nearby. Houthi forces on Yemen’s Red Sea coast have attacked shipping since late 2023.</t>
         </is>
       </c>
     </row>
@@ -6857,7 +7250,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>India and the Gulf shipping diesel into the EU.</t>
+          <t>India -&gt; EU; Gulf refiners -&gt; EU; Russia -&gt; UAE (Fujairah); Russia -&gt; Singapore</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Egypt — run by the Suez Canal Authority.</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7273,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The gateway to the Singapore hub and all of East Asia.</t>
+          <t>India -&gt; Singapore / Indonesia; Gulf refiners -&gt; Asia; Russia -&gt; Singapore</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia, Indonesia and Singapore, which patrol it jointly.</t>
         </is>
       </c>
     </row>
@@ -6893,7 +7296,81 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>US Gulf Coast products heading to Pacific Latin America.</t>
+          <t>USA -&gt; Pacific Latin America; USA -&gt; Asia (South Korea, China)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Panama — run by the Panama Canal Authority since the 1999 US handover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Cape of Good Hope</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>-34.4</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>India -&gt; EU and Gulf refiners -&gt; EU (Red Sea diversions); India -&gt; Brazil / West Africa / US East Coast</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>South Africa holds the coast, but ships sail in open ocean — no country can close it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Danish Straits</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Russia (Baltic) -&gt; West Africa; Russia (Baltic) -&gt; Brazil</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Denmark (and Sweden on the Øresund). Free passage is guaranteed by the 1857 Copenhagen Convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Turkish Straits</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Russia (Black Sea) -&gt; Turkey / Israel / UAE (Fujairah) / Singapore</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Turkey — passage is governed by the 1936 Montreux Convention.</t>
         </is>
       </c>
     </row>

--- a/OILmap/refined.xlsx
+++ b/OILmap/refined.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export flows" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export-Import % (map data)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chokepoints" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; method" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Groups" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Export flows" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Export-Import % (map data)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chokepoints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Notes &amp; method" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Diesel/gasoil, rerouted away from the EU after the 2023 product embargo.</t>
+          <t>Diesel/gasoil, rerouted away from the EU after the 2023 product embargo. US diesel supply announced Oct 9, 2026; delivered volumes unconfirmed.</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2434,6 +2434,48 @@
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>~Sept 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Russia (illustrative Baltic origin)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>USA (illustrative East Coast destination)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Unknown — announced supply, no confirmed US-delivered volume/share</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Baltic -&gt; Danish Straits -&gt; North Atlantic -&gt; US East Coast (illustrative; ports unconfirmed)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Danish Straits (illustrative Baltic routing)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Long dashed — announced</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>OFAC GL 135 dated Oct 9, 2026; US diesel imports authorized through 12:01 a.m. EDT Apr 7, 2027. https://ofac.treasury.gov/media/937216/download?inline= Announcement: https://apnews.com/article/12baccc7aade559bf329079b0548c9da</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Checked Oct 11, 2026</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2723,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern is well established; exact % is this project’s estimate September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2748,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Pattern: East Coast gasoline blendstock; % estimated</t>
+          <t>Pattern: East Coast gasoline blendstock; % estimated September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2773,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2798,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Estimated September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2823,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder</t>
+          <t>Estimated remainder September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3148,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Turkey became Russia’s largest diesel buyer post-2022; % estimated</t>
+          <t>Pattern: Turkey became Russia’s largest diesel buyer post-2022; % estimated September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3173,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern is well established; exact % is this project’s estimate September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3198,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Pattern is well established; exact % is this project’s estimate</t>
+          <t>Pattern is well established; exact % is this project’s estimate September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3223,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Pattern: Brazil became a major Russian diesel buyer post-2022; % estimated</t>
+          <t>Pattern: Brazil became a major Russian diesel buyer post-2022; % estimated September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3248,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Estimated: ~half of Israel’s small refined-import volume</t>
+          <t>Estimated: ~half of Israel’s small refined-import volume September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3273,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Estimated remainder (shadow-fleet cargoes are hard to track)</t>
+          <t>Estimated remainder (shadow-fleet cargoes are hard to track) September baseline; announced Russia -&gt; USA diesel flow has unknown share and is excluded from these percentages. https://ofac.treasury.gov/media/937216/download?inline=</t>
         </is>
       </c>
     </row>
@@ -7135,6 +7177,7 @@
         </is>
       </c>
     </row>
+    <row r="188"/>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
@@ -7342,7 +7385,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Russia (Baltic) -&gt; West Africa; Russia (Baltic) -&gt; Brazil</t>
+          <t>Russia (Baltic) -&gt; West Africa; Russia (Baltic) -&gt; Brazil; Russia -&gt; USA diesel (announced; illustrative Baltic routing only)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7385,7 +7428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7488,6 +7531,18 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Russia -&gt; USA diesel, Oct 9 announcement</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Oct 9, 2026: announced Russia → USA diesel supply. OFAC GL 135 permits Russian diesel imports through 12:01 a.m. EDT April 7, 2027. Delivered US volumes and trade share are unconfirmed; percentages below retain the September baseline. Long-dashed route distinguishes announced supply from established flows. Baltic loading and US East Coast destination are illustrative, not confirmed ports. License applies to diesel; no broader petroleum reopening is inferred. Source: https://ofac.treasury.gov/media/937216/download?inline=</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
